--- a/data/trans_bre/P16A_n_R3-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P16A_n_R3-Edad-trans_bre.xlsx
@@ -665,7 +665,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,64</t>
+          <t>0,0; 1,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,55</t>
+          <t>0,0; 2,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 0,86</t>
+          <t>-0,12; 0,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 0,87</t>
+          <t>-1,1; 0,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 1,27</t>
+          <t>-0,16; 1,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,74</t>
+          <t>-1,46; 0,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 1,45</t>
+          <t>-0,27; 1,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 2,11</t>
+          <t>-0,49; 1,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,0</t>
+          <t>0,0; 0,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 1,49</t>
+          <t>-1,15; 1,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
+          <t>-65,82; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>-50,8; 656,57</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-41,38; 788,3</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-58,1; 302,89</t>
+          <t>-58,41; 349,18</t>
         </is>
       </c>
     </row>
@@ -960,32 +960,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 2,56</t>
+          <t>-0,45; 2,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 3,33</t>
+          <t>0,18; 3,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,29</t>
+          <t>1,36; 4,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,26; 6,9</t>
+          <t>1,28; 6,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-41,29; 859,67</t>
+          <t>-48,21; 722,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,45; 782,41</t>
+          <t>-8,58; 915,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>31,86; 510,52</t>
+          <t>30,97; 512,99</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 5,87</t>
+          <t>0,71; 6,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,23; 8,64</t>
+          <t>3,28; 8,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,13; 7,11</t>
+          <t>1,26; 6,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,21; 7,37</t>
+          <t>2,39; 7,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,2; 774,2</t>
+          <t>11,0; 623,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>118,24; 2431,55</t>
+          <t>131,44; 2387,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,52; 439,3</t>
+          <t>11,2; 445,5</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>28,13; 159,73</t>
+          <t>28,01; 168,22</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 6,54</t>
+          <t>-0,73; 6,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,01; 11,97</t>
+          <t>3,3; 12,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,01; 9,25</t>
+          <t>0,78; 8,91</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 9,14</t>
+          <t>-7,02; 8,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 251,53</t>
+          <t>-18,22; 254,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>30,02; 382,93</t>
+          <t>42,64; 418,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,03; 220,09</t>
+          <t>6,69; 205,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-54,6; 90,68</t>
+          <t>-55,45; 83,34</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 2,36</t>
+          <t>-7,3; 2,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,12; 13,0</t>
+          <t>0,76; 12,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,59; 10,78</t>
+          <t>0,75; 10,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,81; 19,11</t>
+          <t>9,2; 18,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-58,59; 39,91</t>
+          <t>-55,12; 53,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,44; 169,17</t>
+          <t>4,08; 152,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,25; 180,06</t>
+          <t>5,35; 164,17</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>46,17; 126,09</t>
+          <t>42,61; 123,9</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,81</t>
+          <t>0,42; 1,8</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,09</t>
+          <t>2,3; 4,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,85; 3,51</t>
+          <t>1,83; 3,54</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,52; 5,62</t>
+          <t>2,72; 5,72</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,91; 147,9</t>
+          <t>21,21; 149,55</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>97,03; 282,46</t>
+          <t>104,48; 277,36</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>91,56; 252,42</t>
+          <t>90,34; 261,09</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>56,87; 152,43</t>
+          <t>56,59; 153,74</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A_n_R3-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P16A_n_R3-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,52</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,85</t>
+          <t>0,0; 1,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,84</t>
+          <t>0,0; 2,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,17</t>
+          <t>-0,14</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-29,85%</t>
+          <t>-25,55%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 0,87</t>
+          <t>-0,21; 0,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 0,95</t>
+          <t>-1,17; 0,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 1,17</t>
+          <t>-0,16; 1,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 0,63</t>
+          <t>-1,18; 0,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,71</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>67,85%</t>
         </is>
       </c>
     </row>
@@ -860,32 +860,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 1,44</t>
+          <t>-0,28; 1,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 1,96</t>
+          <t>-0,46; 2,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,88</t>
+          <t>0,0; 0,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 1,57</t>
+          <t>-0,65; 1,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-65,82; —</t>
+          <t>-66,31; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-50,8; 656,57</t>
+          <t>-55,72; 763,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-58,41; 349,18</t>
+          <t>-40,46; 519,18</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,45</t>
+          <t>2,17</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>139,18%</t>
+          <t>65,17%</t>
         </is>
       </c>
     </row>
@@ -960,32 +960,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 2,58</t>
+          <t>-0,51; 2,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 3,36</t>
+          <t>0,11; 3,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,19</t>
+          <t>1,42; 4,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 6,22</t>
+          <t>0,13; 4,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-48,21; 722,33</t>
+          <t>-47,33; 633,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 915,99</t>
+          <t>-20,27; 633,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30,97; 512,99</t>
+          <t>2,07; 167,79</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,91</t>
+          <t>5,22</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>87,96%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,71; 6,06</t>
+          <t>0,5; 5,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,28; 8,32</t>
+          <t>3,31; 8,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,26; 6,74</t>
+          <t>1,18; 6,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,39; 7,84</t>
+          <t>2,38; 7,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,0; 623,02</t>
+          <t>2,04; 582,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>131,44; 2387,04</t>
+          <t>138,84; 2447,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,2; 445,5</t>
+          <t>20,05; 456,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>28,01; 168,22</t>
+          <t>30,77; 165,9</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,47</t>
+          <t>8,61</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>85,57%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 6,28</t>
+          <t>-0,25; 6,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,3; 12,74</t>
+          <t>3,28; 12,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,78; 8,91</t>
+          <t>0,68; 9,03</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 8,55</t>
+          <t>4,95; 12,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-18,22; 254,45</t>
+          <t>-12,27; 258,52</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>42,64; 418,26</t>
+          <t>35,25; 403,43</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,69; 205,54</t>
+          <t>6,22; 200,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-55,45; 83,34</t>
+          <t>43,07; 148,61</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14,45</t>
+          <t>13,88</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>74,2%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 2,91</t>
+          <t>-7,44; 2,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,76; 12,13</t>
+          <t>1,07; 13,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,75; 10,32</t>
+          <t>0,28; 10,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,2; 18,89</t>
+          <t>8,84; 18,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-55,12; 53,36</t>
+          <t>-60,15; 33,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,08; 152,5</t>
+          <t>6,57; 182,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,35; 164,17</t>
+          <t>-1,21; 165,17</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>42,61; 123,9</t>
+          <t>41,25; 118,65</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4,36</t>
+          <t>4,8</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>101,37%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,8</t>
+          <t>0,46; 1,83</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,08</t>
+          <t>2,31; 4,09</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,83; 3,54</t>
+          <t>1,89; 3,55</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,72; 5,72</t>
+          <t>3,82; 5,85</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>21,21; 149,55</t>
+          <t>22,95; 147,79</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>104,48; 277,36</t>
+          <t>103,59; 291,27</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>90,34; 261,09</t>
+          <t>89,32; 254,89</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>56,59; 153,74</t>
+          <t>71,61; 134,68</t>
         </is>
       </c>
     </row>
